--- a/5/search/FY3_Missile3_results/solutions_direction_144.0.xlsx
+++ b/5/search/FY3_Missile3_results/solutions_direction_144.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,34 +490,34 @@
         <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6420.495842028141</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F2" t="n">
-        <v>-345.0937404802698</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6446.7768321549</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="I2" t="n">
-        <v>-179.1620992602867</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="J2" t="n">
-        <v>680.4</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6429.256172070393</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="F3" t="n">
-        <v>-289.7831934069422</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6444.586749644336</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="I3" t="n">
-        <v>-192.9897360286188</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="J3" t="n">
-        <v>695.1</v>
+        <v>700</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -560,136 +560,136 @@
         <v>81</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>138</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>6431.008238078844</v>
+        <v>6431.759123511038</v>
       </c>
       <c r="F4" t="n">
-        <v>-278.7210839922764</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6448.966914665463</v>
+        <v>6453.347079686589</v>
       </c>
       <c r="I4" t="n">
-        <v>-165.3344624919546</v>
+        <v>-137.6791889552907</v>
       </c>
       <c r="J4" t="n">
         <v>695.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81</v>
+        <v>85.5</v>
       </c>
       <c r="B5" t="n">
-        <v>120.4</v>
+        <v>110</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6452.033030180251</v>
+        <v>6207.13201272151</v>
       </c>
       <c r="F5" t="n">
-        <v>-145.9757710162899</v>
+        <v>-368.1382389445425</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6452.033030180251</v>
+        <v>6224.393013781636</v>
       </c>
       <c r="I5" t="n">
-        <v>-145.9757710162899</v>
+        <v>-148.8164255232544</v>
       </c>
       <c r="J5" t="n">
-        <v>700</v>
+        <v>680.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B6" t="n">
-        <v>128.8</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6000</v>
+        <v>6210.898049316447</v>
       </c>
       <c r="F6" t="n">
-        <v>-424</v>
+        <v>-320.286206925352</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6000</v>
+        <v>6219.685468037966</v>
       </c>
       <c r="I6" t="n">
-        <v>-166.4</v>
+        <v>-208.6314655472416</v>
       </c>
       <c r="J6" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99</v>
+        <v>85.5</v>
       </c>
       <c r="B7" t="n">
-        <v>120.4</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>5623.305808183124</v>
+        <v>6222.196159101257</v>
       </c>
       <c r="F7" t="n">
-        <v>-621.6464758469083</v>
+        <v>-176.7301108677816</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>5547.966969819749</v>
+        <v>6222.196159101257</v>
       </c>
       <c r="I7" t="n">
-        <v>-145.9757710162899</v>
+        <v>-176.7301108677816</v>
       </c>
       <c r="J7" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -697,139 +697,139 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108</v>
+        <v>85.5</v>
       </c>
       <c r="B8" t="n">
-        <v>103.6</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>5231.660145186131</v>
+        <v>6203.993648892397</v>
       </c>
       <c r="F8" t="n">
-        <v>-635.2930778837299</v>
+        <v>-408.0149322938673</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>5071.589342099908</v>
+        <v>6224.393013781637</v>
       </c>
       <c r="I8" t="n">
-        <v>-142.6458024428404</v>
+        <v>-148.8164255232541</v>
       </c>
       <c r="J8" t="n">
-        <v>577.5</v>
+        <v>680.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108</v>
+        <v>85.5</v>
       </c>
       <c r="B9" t="n">
-        <v>120.4</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5255.887077545127</v>
+        <v>6213.408740379738</v>
       </c>
       <c r="F9" t="n">
-        <v>-709.8559087612698</v>
+        <v>-288.384852245892</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>5069.858846931409</v>
+        <v>6224.079177398726</v>
       </c>
       <c r="I9" t="n">
-        <v>-137.3198859515873</v>
+        <v>-152.8040948581866</v>
       </c>
       <c r="J9" t="n">
-        <v>577.5</v>
+        <v>695.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>106.4</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4840.689859865093</v>
+        <v>6000</v>
       </c>
       <c r="F10" t="n">
-        <v>-724.7257398325837</v>
+        <v>-456</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>4550.862324831367</v>
+        <v>6000</v>
       </c>
       <c r="I10" t="n">
-        <v>-155.9071747907296</v>
+        <v>-138</v>
       </c>
       <c r="J10" t="n">
-        <v>523.6</v>
+        <v>655.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B11" t="n">
-        <v>114.8</v>
+        <v>108</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>4380.534072883778</v>
+        <v>6000</v>
       </c>
       <c r="F11" t="n">
-        <v>-770.9963770981449</v>
+        <v>-408</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>3908.189844141547</v>
+        <v>6000</v>
       </c>
       <c r="I11" t="n">
-        <v>-120.8703204184371</v>
+        <v>-192</v>
       </c>
       <c r="J11" t="n">
-        <v>459.9</v>
+        <v>680.4</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -837,34 +837,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B12" t="n">
-        <v>134.4</v>
+        <v>128</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>4420.033241837833</v>
+        <v>6000</v>
       </c>
       <c r="F12" t="n">
-        <v>-825.3623191201414</v>
+        <v>-440</v>
       </c>
       <c r="G12" t="n">
         <v>700</v>
       </c>
       <c r="H12" t="n">
-        <v>3867.044876481074</v>
+        <v>6000</v>
       </c>
       <c r="I12" t="n">
-        <v>-64.23913081219098</v>
+        <v>-184</v>
       </c>
       <c r="J12" t="n">
-        <v>459.9</v>
+        <v>680.4</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -872,34 +872,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="B13" t="n">
-        <v>128.8</v>
+        <v>134</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3814.191517996144</v>
+        <v>6000</v>
       </c>
       <c r="F13" t="n">
-        <v>-814.1915179961438</v>
+        <v>-320</v>
       </c>
       <c r="G13" t="n">
         <v>700</v>
       </c>
       <c r="H13" t="n">
-        <v>3085.588690661526</v>
+        <v>6000</v>
       </c>
       <c r="I13" t="n">
-        <v>-85.58869066152511</v>
+        <v>-186</v>
       </c>
       <c r="J13" t="n">
-        <v>386.4</v>
+        <v>695.1</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -907,69 +907,69 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>144</v>
+        <v>94.5</v>
       </c>
       <c r="B14" t="n">
-        <v>100.8</v>
+        <v>124</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2738.043478680213</v>
+        <v>5805.421442594945</v>
       </c>
       <c r="F14" t="n">
-        <v>-630.0498627567476</v>
+        <v>-527.6450123418426</v>
       </c>
       <c r="G14" t="n">
         <v>700</v>
       </c>
       <c r="H14" t="n">
-        <v>1922.554348350266</v>
+        <v>5776.234658984186</v>
       </c>
       <c r="I14" t="n">
-        <v>-37.56232844593455</v>
+        <v>-156.791764193119</v>
       </c>
       <c r="J14" t="n">
-        <v>209.9999999999999</v>
+        <v>655.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="B15" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2738.043478680213</v>
+        <v>5617.048429581515</v>
       </c>
       <c r="F15" t="n">
-        <v>-630.0498627567481</v>
+        <v>-582.1389422231027</v>
       </c>
       <c r="G15" t="n">
         <v>700</v>
       </c>
       <c r="H15" t="n">
-        <v>1831.944444980272</v>
+        <v>5553.223167845101</v>
       </c>
       <c r="I15" t="n">
-        <v>28.26961981082195</v>
+        <v>-179.1620992602865</v>
       </c>
       <c r="J15" t="n">
-        <v>209.9999999999999</v>
+        <v>621.6</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -977,34 +977,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>144</v>
+        <v>103.5</v>
       </c>
       <c r="B16" t="n">
-        <v>123.2</v>
+        <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>2810.531401376208</v>
+        <v>5428.525749280744</v>
       </c>
       <c r="F16" t="n">
-        <v>-682.7154213621538</v>
+        <v>-619.6384348664874</v>
       </c>
       <c r="G16" t="n">
         <v>700</v>
       </c>
       <c r="H16" t="n">
-        <v>1813.822464306273</v>
+        <v>5309.468613714233</v>
       </c>
       <c r="I16" t="n">
-        <v>41.43600946217305</v>
+        <v>-123.7297754636723</v>
       </c>
       <c r="J16" t="n">
-        <v>209.9999999999999</v>
+        <v>577.5</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1012,36 +1012,386 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>120</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5439.731126745827</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-666.3121910455761</v>
+      </c>
+      <c r="G17" t="n">
+        <v>700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5299.663908432284</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-82.89023880697016</v>
+      </c>
+      <c r="J17" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B18" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5258.359213500126</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-717.4643608916313</v>
+      </c>
+      <c r="G18" t="n">
+        <v>700</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5072.949016875158</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-146.8304511145391</v>
+      </c>
+      <c r="J18" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>122</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5066.252425029181</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-745.7339406724604</v>
+      </c>
+      <c r="G19" t="n">
+        <v>700</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4786.128152537935</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-69.45412287419856</v>
+      </c>
+      <c r="J19" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117</v>
+      </c>
+      <c r="B20" t="n">
+        <v>108</v>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4823.256624675095</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-690.5110893037504</v>
+      </c>
+      <c r="G20" t="n">
+        <v>700</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4529.070780843868</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-113.138861629688</v>
+      </c>
+      <c r="J20" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117</v>
+      </c>
+      <c r="B21" t="n">
+        <v>124</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4874.103560645925</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-790.3038200128476</v>
+      </c>
+      <c r="G21" t="n">
+        <v>700</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4536.334628839702</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-127.3949660167018</v>
+      </c>
+      <c r="J21" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126</v>
+      </c>
+      <c r="B22" t="n">
+        <v>134</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4424.735523856172</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-831.8344550751408</v>
+      </c>
+      <c r="G22" t="n">
+        <v>700</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3873.392957205832</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-72.97651435144007</v>
+      </c>
+      <c r="J22" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108</v>
+      </c>
+      <c r="C23" t="n">
+        <v>28</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4036.069101849525</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-700.532360025506</v>
+      </c>
+      <c r="G23" t="n">
+        <v>700</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3474.945988092246</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-43.54160574707919</v>
+      </c>
+      <c r="J23" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3323.371001087891</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-713.9428698777533</v>
+      </c>
+      <c r="G24" t="n">
+        <v>700</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2570.569095143861</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-70.98930203087139</v>
+      </c>
+      <c r="J24" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B25" t="n">
+        <v>124</v>
+      </c>
+      <c r="C25" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3359.870487436693</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-745.1163761976018</v>
+      </c>
+      <c r="G25" t="n">
+        <v>700</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2511.257429827058</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-20.33235426111662</v>
+      </c>
+      <c r="J25" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>140</v>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3445.035955583896</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-817.8545576105826</v>
+      </c>
+      <c r="G26" t="n">
+        <v>700</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2486.924438927857</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4499832854489796</v>
+      </c>
+      <c r="J26" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>144</v>
       </c>
-      <c r="B17" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="B27" t="n">
+        <v>112</v>
+      </c>
+      <c r="C27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
-        <v>2892.080314409202</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-741.9641747932346</v>
-      </c>
-      <c r="G17" t="n">
-        <v>700</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1782.108998126775</v>
-      </c>
-      <c r="I17" t="n">
-        <v>64.47719135203863</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="E27" t="n">
+        <v>2738.043478680213</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-630.0498627567481</v>
+      </c>
+      <c r="G27" t="n">
+        <v>700</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1831.944444980272</v>
+      </c>
+      <c r="I27" t="n">
+        <v>28.26961981082195</v>
+      </c>
+      <c r="J27" t="n">
         <v>209.9999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K27" t="n">
         <v>1</v>
       </c>
     </row>
